--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_2.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_2.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Smoker?</t>
+          <t>Treatment3</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Interesting</t>
+          <t>Happiness</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.5629855804112014</v>
+        <v>-0.8236936853404271</v>
       </c>
       <c r="C2">
-        <v>-1.344963082793369</v>
+        <v>-0.006907810614867504</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.9171052714739473</v>
+        <v>-0.4527860805241414</v>
       </c>
       <c r="C3">
-        <v>-2.159059115565262</v>
+        <v>-0.955908385247894</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2950732647574735</v>
+        <v>-0.4991036563192565</v>
       </c>
       <c r="C4">
-        <v>2.797646994377934</v>
+        <v>-0.01306943079422596</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.2753446366124284</v>
+        <v>0.2848914028291118</v>
       </c>
       <c r="C5">
-        <v>0.8092465095920514</v>
+        <v>1.335934122567654</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.3790878335389527</v>
+        <v>-0.2125711935628453</v>
       </c>
       <c r="C6">
-        <v>-1.45899073105376</v>
+        <v>-0.6954721210128683</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.263766204046915</v>
+        <v>2.64399150884726</v>
       </c>
       <c r="C7">
-        <v>-0.1491153702663142</v>
+        <v>-0.9246285635659626</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3780117683060147</v>
+        <v>1.877932087323866</v>
       </c>
       <c r="C8">
-        <v>0.3333498439786683</v>
+        <v>0.02412114586025949</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.893147505806842</v>
+        <v>1.351152657457</v>
       </c>
       <c r="C9">
-        <v>1.806722361705252</v>
+        <v>-2.067952644214109</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.8332811992848088</v>
+        <v>0.07673398208713972</v>
       </c>
       <c r="C10">
-        <v>-0.6376452551061885</v>
+        <v>-0.4613327816601034</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.01592679375222</v>
+        <v>0.2682569819958279</v>
       </c>
       <c r="C11">
-        <v>0.6888825235688785</v>
+        <v>-1.834492474931904</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.6930425372100525</v>
+        <v>0.1963162656440319</v>
       </c>
       <c r="C12">
-        <v>0.3835077056308299</v>
+        <v>-0.2611432710935628</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.09565485859886404</v>
+        <v>0.3754733761086166</v>
       </c>
       <c r="C13">
-        <v>-0.2594009118644069</v>
+        <v>-0.6594063949394573</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.5555831185517127</v>
+        <v>-0.5544403929785525</v>
       </c>
       <c r="C14">
-        <v>-0.6865661926230896</v>
+        <v>1.601386172719342</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.782741459211885</v>
+        <v>1.022718175200386</v>
       </c>
       <c r="C15">
-        <v>1.040937064808684</v>
+        <v>-1.119994848073637</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.790447656588234</v>
+        <v>0.446684295759666</v>
       </c>
       <c r="C16">
-        <v>0.9661693256880453</v>
+        <v>-1.83273819567211</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.008371941199163433</v>
+        <v>-1.130397559622289</v>
       </c>
       <c r="C17">
-        <v>0.5534576880888769</v>
+        <v>0.7791183120371196</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.7281824427202186</v>
+        <v>-0.2765185133812382</v>
       </c>
       <c r="C18">
-        <v>-1.880178531666464</v>
+        <v>2.206373229441014</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.3635754396676696</v>
+        <v>-1.11495012797157</v>
       </c>
       <c r="C19">
-        <v>-1.723463432718146</v>
+        <v>0.149914532488446</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.976320762815165</v>
+        <v>-1.148758731592988</v>
       </c>
       <c r="C20">
-        <v>-0.8380088278841715</v>
+        <v>0.4223469860380904</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.5028241664695606</v>
+        <v>0.8626647691753883</v>
       </c>
       <c r="C21">
-        <v>1.886808702729081</v>
+        <v>1.108692713232418</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.404770759965357</v>
+        <v>0.3522785603491696</v>
       </c>
       <c r="C22">
-        <v>-0.912806381772838</v>
+        <v>-0.1333491253960191</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.6346674699252052</v>
+        <v>-0.3219028527627069</v>
       </c>
       <c r="C23">
-        <v>-0.08861873197233927</v>
+        <v>1.308927902615538</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.7977574816364419</v>
+        <v>0.08915412114880308</v>
       </c>
       <c r="C24">
-        <v>-0.9887048165075618</v>
+        <v>0.2126640135183018</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-1.037765962432313</v>
+        <v>-0.5888585526965092</v>
       </c>
       <c r="C25">
-        <v>-0.2163729996069083</v>
+        <v>-1.809700566272991</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.655886020430562</v>
+        <v>-0.3927713906556905</v>
       </c>
       <c r="C26">
-        <v>-0.3166571745353449</v>
+        <v>0.8325500782597948</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.372764378872498</v>
+        <v>0.5136224219069206</v>
       </c>
       <c r="C27">
-        <v>-0.6470588429158797</v>
+        <v>-0.08418553501938225</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.074464165581147</v>
+        <v>0.3814461566206235</v>
       </c>
       <c r="C28">
-        <v>0.6240610291054748</v>
+        <v>-0.3190271948401066</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.9614680167423977</v>
+        <v>-0.494075392665875</v>
       </c>
       <c r="C29">
-        <v>0.07058782545222864</v>
+        <v>0.5196408142516988</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.1451206723746231</v>
+        <v>1.187300435116705</v>
       </c>
       <c r="C30">
-        <v>-0.02912859699919194</v>
+        <v>-0.5808232167174818</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.3264772169569499</v>
+        <v>0.1010017370511221</v>
       </c>
       <c r="C31">
-        <v>1.976156713243911</v>
+        <v>0.9094308005662732</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.437528908938355</v>
+        <v>0.8276933554343738</v>
       </c>
       <c r="C32">
-        <v>-0.21813551776964</v>
+        <v>-1.304657516946114</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>2.454388516805464</v>
+        <v>-0.5172820338492811</v>
       </c>
       <c r="C33">
-        <v>0.2745806288613815</v>
+        <v>0.801500483633564</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.8535300353369718</v>
+        <v>0.9260428460312372</v>
       </c>
       <c r="C34">
-        <v>1.743241373188777</v>
+        <v>0.6404072097086716</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.143764339033628</v>
+        <v>0.3545237131925041</v>
       </c>
       <c r="C35">
-        <v>0.4374319512337763</v>
+        <v>0.4397422827653057</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.687364797212949</v>
+        <v>-1.087446413401636</v>
       </c>
       <c r="C36">
-        <v>0.6195845312871321</v>
+        <v>0.8076759377630441</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.2984234258433653</v>
+        <v>0.762474646363105</v>
       </c>
       <c r="C37">
-        <v>-0.2827683397734539</v>
+        <v>0.5873296263012981</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-1.036574053203887</v>
+        <v>0.1043914316799253</v>
       </c>
       <c r="C38">
-        <v>0.6024304816051009</v>
+        <v>0.8032050915561647</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-1.560142564615058</v>
+        <v>-1.02537634204055</v>
       </c>
       <c r="C39">
-        <v>-0.0525954011041847</v>
+        <v>0.6217292689556813</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.04262130411134667</v>
+        <v>0.1376025770056157</v>
       </c>
       <c r="C40">
-        <v>0.3208878433882583</v>
+        <v>0.4917519020526702</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.784754931495869</v>
+        <v>0.9857290466541437</v>
       </c>
       <c r="C41">
-        <v>1.10606472085986</v>
+        <v>0.2243619346105089</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.03375490139867605</v>
+        <v>0.7095234858930519</v>
       </c>
       <c r="C42">
-        <v>0.841732706725917</v>
+        <v>0.04026165318110309</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.1810901331001302</v>
+        <v>-0.6721339384450283</v>
       </c>
       <c r="C43">
-        <v>1.16768315300035</v>
+        <v>-0.563844305055242</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.7512727126366598</v>
+        <v>1.091926427183766</v>
       </c>
       <c r="C44">
-        <v>0.594566889119159</v>
+        <v>0.3100118999157213</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.6817045656389523</v>
+        <v>0.02815780792350971</v>
       </c>
       <c r="C45">
-        <v>-1.057061017091814</v>
+        <v>1.4237520775994</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.079812545372665</v>
+        <v>-2.218858469894466</v>
       </c>
       <c r="C46">
-        <v>1.292326290653697</v>
+        <v>1.707166951303061</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.2348355440023865</v>
+        <v>-0.2068940573879692</v>
       </c>
       <c r="C47">
-        <v>-0.660026560201193</v>
+        <v>-0.9896092788058937</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.2612847802857181</v>
+        <v>0.937580122834742</v>
       </c>
       <c r="C48">
-        <v>0.4985103879389834</v>
+        <v>0.5981305005847315</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.342495532177092</v>
+        <v>-0.8701392177355924</v>
       </c>
       <c r="C49">
-        <v>-0.1140774984588723</v>
+        <v>0.285845264048299</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.267442645773345</v>
+        <v>-1.326781822170503</v>
       </c>
       <c r="C50">
-        <v>-1.258591031006685</v>
+        <v>1.005107281646586</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.6248881053155995</v>
+        <v>1.469674380315792</v>
       </c>
       <c r="C51">
-        <v>-0.4182748997547386</v>
+        <v>0.692581157166191</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.2299190700807446</v>
+        <v>0.3553347385083788</v>
       </c>
       <c r="C52">
-        <v>-0.3610786687160523</v>
+        <v>-0.1563189411187093</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>1.395505062933435</v>
+        <v>-1.43366901530229</v>
       </c>
       <c r="C53">
-        <v>0.1790546210933503</v>
+        <v>1.086906322821491</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>1.221635985640855</v>
+        <v>0.4285046357368753</v>
       </c>
       <c r="C54">
-        <v>1.150956194746</v>
+        <v>-0.1711362412482399</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.3071898746751978</v>
+        <v>-0.8111508360892973</v>
       </c>
       <c r="C55">
-        <v>-1.179239531113</v>
+        <v>-0.01683115439296895</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.2291605461424675</v>
+        <v>2.250121875730126</v>
       </c>
       <c r="C56">
-        <v>-0.8101419206657158</v>
+        <v>-0.3503413177138998</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>1.048236669958408</v>
+        <v>1.022440742740762</v>
       </c>
       <c r="C57">
-        <v>1.912060017825881</v>
+        <v>-0.07149917331772615</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.6261840516237361</v>
+        <v>0.07903778569347968</v>
       </c>
       <c r="C58">
-        <v>-0.1935853866455834</v>
+        <v>0.3284240310712512</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>1.793999445524473</v>
+        <v>0.4607490179546441</v>
       </c>
       <c r="C59">
-        <v>0.2868036716522478</v>
+        <v>-0.1736271521974593</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-1.325099376399965</v>
+        <v>0.4606454901422936</v>
       </c>
       <c r="C60">
-        <v>0.1099738019287403</v>
+        <v>1.108491981860743</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.9972998989749045</v>
+        <v>1.323207705332892</v>
       </c>
       <c r="C61">
-        <v>0.3411038551001596</v>
+        <v>0.3074055563830836</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.2625324496628431</v>
+        <v>0.150807772050409</v>
       </c>
       <c r="C62">
-        <v>0.03317874121482732</v>
+        <v>-1.414646494504737</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.02155522303189213</v>
+        <v>-1.392337064084105</v>
       </c>
       <c r="C63">
-        <v>-0.4001368813565598</v>
+        <v>-2.93897758417961</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.3913132709543356</v>
+        <v>-0.3663198537182363</v>
       </c>
       <c r="C64">
-        <v>-0.3057417182195896</v>
+        <v>1.692748086484027</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.023925069100954</v>
+        <v>-0.4182054459717576</v>
       </c>
       <c r="C65">
-        <v>-0.7858657969011158</v>
+        <v>-0.5085948981920575</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-0.1852566977468499</v>
+        <v>0.598848709929687</v>
       </c>
       <c r="C66">
-        <v>-0.8723967022942722</v>
+        <v>-1.114437385382054</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.2541249359173732</v>
+        <v>-1.578626143628164</v>
       </c>
       <c r="C67">
-        <v>1.156640848152885</v>
+        <v>3.050084199392288</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-1.368154265452477</v>
+        <v>1.723554668969323</v>
       </c>
       <c r="C68">
-        <v>-1.273378447092439</v>
+        <v>0.6897717480671455</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.3091543523106156</v>
+        <v>0.2780723745373875</v>
       </c>
       <c r="C69">
-        <v>0.3697626080076373</v>
+        <v>-1.00835377474497</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.7331934396446119</v>
+        <v>2.317774973715129</v>
       </c>
       <c r="C70">
-        <v>1.240529375088808</v>
+        <v>-1.484520564451646</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.6393577112747821</v>
+        <v>1.921708057857831</v>
       </c>
       <c r="C71">
-        <v>1.007000653537118</v>
+        <v>-0.8812793130618789</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.6302640419074044</v>
+        <v>0.7936156082010301</v>
       </c>
       <c r="C72">
-        <v>0.9408560588990749</v>
+        <v>0.5195053797252112</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.6151776068085347</v>
+        <v>-0.7078810205581939</v>
       </c>
       <c r="C73">
-        <v>-1.085847846435604</v>
+        <v>-1.096258209485804</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.3625875251733418</v>
+        <v>1.582798559648045</v>
       </c>
       <c r="C74">
-        <v>-0.1009780638590646</v>
+        <v>0.02760034573063352</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-1.336076256925953</v>
+        <v>-1.697460754213708</v>
       </c>
       <c r="C75">
-        <v>-2.076958902357034</v>
+        <v>1.427859124908939</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>-0.127705823584418</v>
+        <v>0.7765290479987548</v>
       </c>
       <c r="C76">
-        <v>-2.63412403554914</v>
+        <v>1.177431819603852</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.3528201627279132</v>
+        <v>-1.293937696784032</v>
       </c>
       <c r="C77">
-        <v>0.6942887084099827</v>
+        <v>1.79417031783397</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.6787029217087086</v>
+        <v>-1.51537328450835</v>
       </c>
       <c r="C78">
-        <v>-0.824652432386936</v>
+        <v>0.001157692188265114</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.7334914463778816</v>
+        <v>-0.3481156342381729</v>
       </c>
       <c r="C79">
-        <v>1.42811245078759</v>
+        <v>-0.9615243481388043</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>1.782044360238722</v>
+        <v>1.147728227907519</v>
       </c>
       <c r="C80">
-        <v>0.7015606996341561</v>
+        <v>-0.2459987061995254</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.3947442815328674</v>
+        <v>-1.258079859893675</v>
       </c>
       <c r="C81">
-        <v>0.7610443542051336</v>
+        <v>0.2630377091398868</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.9235904255539708</v>
+        <v>-1.103760438997505</v>
       </c>
       <c r="C82">
-        <v>-1.382645204481832</v>
+        <v>1.50269660436243</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>1.180708317012644</v>
+        <v>0.7018284829474133</v>
       </c>
       <c r="C83">
-        <v>1.536716790307456</v>
+        <v>-1.585619173456016</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.1744413111880814</v>
+        <v>-1.119932461653163</v>
       </c>
       <c r="C84">
-        <v>-1.283657557744438</v>
+        <v>-0.2016146873107029</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-0.7169514164474485</v>
+        <v>0.1905738230542982</v>
       </c>
       <c r="C85">
-        <v>-0.1908969197919836</v>
+        <v>-2.375224091669049</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>1.33546273841631</v>
+        <v>0.6531747583047803</v>
       </c>
       <c r="C86">
-        <v>-0.1544589764223836</v>
+        <v>-0.8917849145961677</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.1578958967815843</v>
+        <v>2.37637225399532</v>
       </c>
       <c r="C87">
-        <v>-0.03534579451254881</v>
+        <v>-0.6834811964687701</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-1.38426657102066</v>
+        <v>1.198683892192098</v>
       </c>
       <c r="C88">
-        <v>-1.02436531032079</v>
+        <v>-0.02114667786147018</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.446510571739096</v>
+        <v>0.1682804743731798</v>
       </c>
       <c r="C89">
-        <v>0.4807665413814757</v>
+        <v>0.563939202003803</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.8386787217096592</v>
+        <v>1.156520324585574</v>
       </c>
       <c r="C90">
-        <v>-0.04855384422020281</v>
+        <v>1.140853868926482</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>-0.6053761746617524</v>
+        <v>-0.9858269832600239</v>
       </c>
       <c r="C91">
-        <v>-0.3088045243088673</v>
+        <v>0.4361221490002097</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.6598485373767039</v>
+        <v>-1.194174683582515</v>
       </c>
       <c r="C92">
-        <v>0.03345574321892775</v>
+        <v>0.7676515327981847</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.3980095564094245</v>
+        <v>0.07529830866019788</v>
       </c>
       <c r="C93">
-        <v>0.6622549263045556</v>
+        <v>-0.3869722592847376</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.4588269694447629</v>
+        <v>-0.165164497689224</v>
       </c>
       <c r="C94">
-        <v>0.7754227944649912</v>
+        <v>0.1410725777892263</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.3388751027081294</v>
+        <v>-0.322693285018694</v>
       </c>
       <c r="C95">
-        <v>-2.156824966461819</v>
+        <v>0.3691320003833642</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.8593319998770732</v>
+        <v>0.44856230396652</v>
       </c>
       <c r="C96">
-        <v>-0.001103656002783893</v>
+        <v>-0.02523511407507528</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.8415938608319279</v>
+        <v>0.1280831537985882</v>
       </c>
       <c r="C97">
-        <v>0.472121403058693</v>
+        <v>-0.5486574824249402</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-0.5675358671888039</v>
+        <v>-2.43480962482794</v>
       </c>
       <c r="C98">
-        <v>-1.303920492354596</v>
+        <v>1.626800909846503</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-2.732784891776392</v>
+        <v>-1.771274383011259</v>
       </c>
       <c r="C99">
-        <v>-2.050184287635706</v>
+        <v>2.939208105300311</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.4476805429786527</v>
+        <v>-0.2975119313346631</v>
       </c>
       <c r="C100">
-        <v>0.6371765919418885</v>
+        <v>0.6734423152621769</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>-1.552919506352772</v>
+        <v>-0.8137311072186566</v>
       </c>
       <c r="C101">
-        <v>-0.1999673064265369</v>
+        <v>2.18847877661673</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.5535090416430274</v>
+        <v>-1.402425323031004</v>
       </c>
       <c r="C102">
-        <v>0.4129519315755509</v>
+        <v>0.05811613147827932</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>-2.053910453353308</v>
+        <v>0.9715187823983252</v>
       </c>
       <c r="C103">
-        <v>-1.427714023627964</v>
+        <v>-1.481080353348578</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>2.127237051355755</v>
+        <v>-0.4129712853232756</v>
       </c>
       <c r="C104">
-        <v>0.6049841827603578</v>
+        <v>-0.09458439459200385</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.3350853566254762</v>
+        <v>0.02847059219793628</v>
       </c>
       <c r="C105">
-        <v>-0.5379379381838011</v>
+        <v>1.261737306682554</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>2.232927545573387</v>
+        <v>1.250052871725351</v>
       </c>
       <c r="C106">
-        <v>1.425655508211324</v>
+        <v>-2.409633544601568</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>0.7716532631366306</v>
+        <v>0.07996263657248931</v>
       </c>
       <c r="C107">
-        <v>2.156634326349867</v>
+        <v>-0.8531157004583826</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.9646318870591118</v>
+        <v>-0.0861389362223772</v>
       </c>
       <c r="C108">
-        <v>-0.5613603220337429</v>
+        <v>1.016519818118162</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.9562768597109894</v>
+        <v>0.239636934808268</v>
       </c>
       <c r="C109">
-        <v>-0.5702822619895012</v>
+        <v>1.724002486430204</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.7600971961536773</v>
+        <v>-0.3123667886953295</v>
       </c>
       <c r="C110">
-        <v>-0.5715217259051623</v>
+        <v>0.8070071867352472</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>-0.1030527283933348</v>
+        <v>-0.01854003893768471</v>
       </c>
       <c r="C111">
-        <v>0.5473835602742063</v>
+        <v>-1.558911221664991</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>-1.258451102958012</v>
+        <v>0.01450553085145949</v>
       </c>
       <c r="C112">
-        <v>-0.5831833396230565</v>
+        <v>-0.1673985547769078</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>3.029136807216826</v>
+        <v>-1.892215218965116</v>
       </c>
       <c r="C113">
-        <v>1.155193287787688</v>
+        <v>-0.5770400967086641</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>-0.01372509746002664</v>
+        <v>0.1925369467922199</v>
       </c>
       <c r="C114">
-        <v>-0.09728626729910385</v>
+        <v>-0.9261213039628636</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>-1.520874540385658</v>
+        <v>-0.6172165522368659</v>
       </c>
       <c r="C115">
-        <v>-2.250660847795725</v>
+        <v>0.4065490898238614</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>-0.01751129801166867</v>
+        <v>-0.9286785417760024</v>
       </c>
       <c r="C116">
-        <v>-0.4950364211065732</v>
+        <v>-0.7233462558008066</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>-2.077518542868703</v>
+        <v>0.4553264406381294</v>
       </c>
       <c r="C117">
-        <v>-0.3815241232540634</v>
+        <v>-0.02243244584647675</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>-0.943396269706078</v>
+        <v>-1.342705567759048</v>
       </c>
       <c r="C118">
-        <v>-0.9306868307206602</v>
+        <v>0.3351094977876139</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>-0.7824480675217356</v>
+        <v>0.6521167234622361</v>
       </c>
       <c r="C119">
-        <v>-0.6071578992568014</v>
+        <v>0.1514837999177788</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>-0.1873439635766606</v>
+        <v>-0.706615652439931</v>
       </c>
       <c r="C120">
-        <v>-0.294220024140033</v>
+        <v>-0.2696554362873122</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.6107922960741951</v>
+        <v>0.3281658655380262</v>
       </c>
       <c r="C121">
-        <v>1.432980062278335</v>
+        <v>-0.5142789143806996</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-0.1716287544675134</v>
+        <v>-0.6064480222888674</v>
       </c>
       <c r="C122">
-        <v>-1.334887176276383</v>
+        <v>1.223321591870447</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.7794386405876431</v>
+        <v>-1.843442584587747</v>
       </c>
       <c r="C123">
-        <v>-1.399091941316722</v>
+        <v>1.128859029677036</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>0.01613530001997768</v>
+        <v>-0.7293551626965412</v>
       </c>
       <c r="C124">
-        <v>-1.44066686455675</v>
+        <v>0.7929090808302595</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.317670285905089</v>
+        <v>-0.197128473195978</v>
       </c>
       <c r="C125">
-        <v>0.06500071721183782</v>
+        <v>-0.3945796424413706</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-0.3946083680143473</v>
+        <v>-0.1852165708458531</v>
       </c>
       <c r="C126">
-        <v>-0.2669991246111655</v>
+        <v>0.6269832883512531</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>0.528819738571528</v>
+        <v>0.05070497803196481</v>
       </c>
       <c r="C127">
-        <v>-0.3475188265715222</v>
+        <v>1.627804523627126</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>0.2708147357302447</v>
+        <v>-0.530655479946905</v>
       </c>
       <c r="C128">
-        <v>1.039933319160929</v>
+        <v>1.737538925123707</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.5747603876511909</v>
+        <v>-0.7245691508530987</v>
       </c>
       <c r="C129">
-        <v>0.2122781454799677</v>
+        <v>-0.7625409937989851</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.9868007558103812</v>
+        <v>-0.3208854434240123</v>
       </c>
       <c r="C130">
-        <v>0.4157716515632661</v>
+        <v>-0.1073277057073222</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>-0.1364052574958511</v>
+        <v>-0.5228571598348886</v>
       </c>
       <c r="C131">
-        <v>1.381885160902887</v>
+        <v>-0.4440477767241195</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.2519337813871175</v>
+        <v>-0.9932487777852093</v>
       </c>
       <c r="C132">
-        <v>0.6372435504342016</v>
+        <v>0.6177036184941602</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>-0.5075474480047947</v>
+        <v>-2.207696197178958</v>
       </c>
       <c r="C133">
-        <v>0.3605234363097272</v>
+        <v>-0.289064837372944</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>-0.2806901357490574</v>
+        <v>-0.6458128860044254</v>
       </c>
       <c r="C134">
-        <v>0.05467886576720482</v>
+        <v>-0.5455799598519134</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.6358955337873656</v>
+        <v>-1.194299056847282</v>
       </c>
       <c r="C135">
-        <v>-0.08562197346952904</v>
+        <v>0.9471310759781619</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>-0.1078705571885929</v>
+        <v>-0.01586946661088287</v>
       </c>
       <c r="C136">
-        <v>-0.01299671075169728</v>
+        <v>-0.02156441086371873</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.1362086225247091</v>
+        <v>0.4514556185012352</v>
       </c>
       <c r="C137">
-        <v>1.159578518609446</v>
+        <v>0.797136598377412</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>-2.0479428568882</v>
+        <v>0.4813925079804978</v>
       </c>
       <c r="C138">
-        <v>-1.836808199460092</v>
+        <v>-0.474295496371599</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>-1.219505766779772</v>
+        <v>-1.631188006109048</v>
       </c>
       <c r="C139">
-        <v>-0.8183519641739032</v>
+        <v>1.559981487856572</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>-0.1109630719413416</v>
+        <v>1.182827920149734</v>
       </c>
       <c r="C140">
-        <v>-0.6109994009422811</v>
+        <v>-0.2228726729829219</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>-1.156818186531731</v>
+        <v>-1.016413028468068</v>
       </c>
       <c r="C141">
-        <v>0.7268449098846945</v>
+        <v>-0.1407396878672667</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-0.82997361596321</v>
+        <v>0.052204914995086</v>
       </c>
       <c r="C142">
-        <v>0.2039057539216322</v>
+        <v>1.321650984230823</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>1.36407079151132</v>
+        <v>0.5236668635888188</v>
       </c>
       <c r="C143">
-        <v>-0.9320225158824202</v>
+        <v>0.2152289731785557</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>-1.305889683715874</v>
+        <v>-0.231973659193392</v>
       </c>
       <c r="C144">
-        <v>-0.8514350845330885</v>
+        <v>1.315343715135478</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>-0.6001140075688788</v>
+        <v>-1.443803861814771</v>
       </c>
       <c r="C145">
-        <v>-0.1899214884851979</v>
+        <v>1.748604148522602</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>0.6290264927525916</v>
+        <v>-0.0738339158598522</v>
       </c>
       <c r="C146">
-        <v>-0.3683120146519154</v>
+        <v>0.3402408048300595</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>-1.101262864297822</v>
+        <v>-0.6554557743059881</v>
       </c>
       <c r="C147">
-        <v>1.190650479451429</v>
+        <v>1.381917311896232</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>0.4205066266003566</v>
+        <v>1.558391737420301</v>
       </c>
       <c r="C148">
-        <v>0.5052646053209201</v>
+        <v>-0.8456518294886475</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-0.1936534467459005</v>
+        <v>0.0480028595608968</v>
       </c>
       <c r="C149">
-        <v>-0.6024868829523582</v>
+        <v>0.2963755865665815</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>-1.110707857555376</v>
+        <v>-1.254557141896455</v>
       </c>
       <c r="C150">
-        <v>0.4339988250103206</v>
+        <v>-0.2729770213514486</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>-1.066869392217425</v>
+        <v>0.3580433790683637</v>
       </c>
       <c r="C151">
-        <v>-1.618540961762284</v>
+        <v>0.1421002837595577</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>0.5938762314967521</v>
+        <v>1.739897205952207</v>
       </c>
       <c r="C152">
-        <v>1.207100916721526</v>
+        <v>-1.026150394896332</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-0.8760339159843964</v>
+        <v>1.154022259777201</v>
       </c>
       <c r="C153">
-        <v>-0.912487106885352</v>
+        <v>0.07355525360382353</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>-1.268159322008502</v>
+        <v>-0.9403146888013864</v>
       </c>
       <c r="C154">
-        <v>-0.8425489202439018</v>
+        <v>-0.5744666198887241</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>-1.313627793945473</v>
+        <v>0.2008534477500876</v>
       </c>
       <c r="C155">
-        <v>-1.069504475110826</v>
+        <v>0.1105282713512359</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.09278497426619392</v>
+        <v>-0.6259974394542387</v>
       </c>
       <c r="C156">
-        <v>1.077077941735731</v>
+        <v>0.09069284738890179</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.3909118050931629</v>
+        <v>-0.2492754445202477</v>
       </c>
       <c r="C157">
-        <v>1.400444995059081</v>
+        <v>0.2872796392695069</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>1.245834302504268</v>
+        <v>0.8833608799940309</v>
       </c>
       <c r="C158">
-        <v>0.06691552582284205</v>
+        <v>0.1277882838890146</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>2.174018415873372</v>
+        <v>0.2231758451889874</v>
       </c>
       <c r="C159">
-        <v>1.123446765977139</v>
+        <v>0.5818624880835892</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>0.1420064781196179</v>
+        <v>1.687611788093135</v>
       </c>
       <c r="C160">
-        <v>0.6213129899647131</v>
+        <v>0.02811928735179414</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>0.1409293380689933</v>
+        <v>-0.5477932708001421</v>
       </c>
       <c r="C161">
-        <v>1.467659380861737</v>
+        <v>-0.3095471384703647</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>1.554756075359193</v>
+        <v>0.7532971190199536</v>
       </c>
       <c r="C162">
-        <v>2.361731168051556</v>
+        <v>0.15980102912559</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>0.9114102535457819</v>
+        <v>0.6553362935481091</v>
       </c>
       <c r="C163">
-        <v>-1.572402211492965</v>
+        <v>-2.328202108735808</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.291944414369196</v>
+        <v>0.5650251200670726</v>
       </c>
       <c r="C164">
-        <v>-0.5840611573105439</v>
+        <v>0.7349936412502276</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>1.218486869121556</v>
+        <v>0.5509621433504512</v>
       </c>
       <c r="C165">
-        <v>0.6491432870381654</v>
+        <v>-0.1931094759385677</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.6729825754928122</v>
+        <v>0.4582613894616795</v>
       </c>
       <c r="C166">
-        <v>0.3394187079694996</v>
+        <v>0.8762662335737961</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-0.5440076387196142</v>
+        <v>0.4344684949879687</v>
       </c>
       <c r="C167">
-        <v>-2.2256994806694</v>
+        <v>-0.9986958805160768</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>-1.020503122177776</v>
+        <v>0.4095721691766174</v>
       </c>
       <c r="C168">
-        <v>-1.793852716355566</v>
+        <v>-0.9887297400676118</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>-0.1780558394517328</v>
+        <v>1.247607933011552</v>
       </c>
       <c r="C169">
-        <v>-1.386764689698779</v>
+        <v>0.3577509953882605</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>-0.05354594896930857</v>
+        <v>0.04406708841843382</v>
       </c>
       <c r="C170">
-        <v>-0.6050672324085009</v>
+        <v>0.01316773473810924</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>0.3826382508710482</v>
+        <v>-0.5582527441218001</v>
       </c>
       <c r="C171">
-        <v>-0.03923871754789002</v>
+        <v>3.55154032276914</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>-0.7946801946214739</v>
+        <v>-0.1012142944951917</v>
       </c>
       <c r="C172">
-        <v>-0.327366545791782</v>
+        <v>1.328603963181816</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>1.566246815086973</v>
+        <v>-0.2279678609179539</v>
       </c>
       <c r="C173">
-        <v>-0.5891736718501568</v>
+        <v>2.5847349687014</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>1.507980057085586</v>
+        <v>-0.1527341271994156</v>
       </c>
       <c r="C174">
-        <v>1.526601693917148</v>
+        <v>0.03634318348281697</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>-0.1585155580360918</v>
+        <v>-1.260731076817456</v>
       </c>
       <c r="C175">
-        <v>0.3189484250868336</v>
+        <v>-0.2798843884616666</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>-0.3976414851756283</v>
+        <v>0.8074227402612427</v>
       </c>
       <c r="C176">
-        <v>-1.454667758654412</v>
+        <v>-1.08255237923119</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>0.8516229946967125</v>
+        <v>-0.4230504957289836</v>
       </c>
       <c r="C177">
-        <v>1.047534496280449</v>
+        <v>0.2567564147469013</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-0.5180231223661248</v>
+        <v>-0.8449285830307292</v>
       </c>
       <c r="C178">
-        <v>-1.020334390359666</v>
+        <v>1.980695178006908</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-0.1898336964681453</v>
+        <v>0.4271914028168894</v>
       </c>
       <c r="C179">
-        <v>-0.6992521086551281</v>
+        <v>1.929363187281979</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>-0.3792609379196196</v>
+        <v>0.5009190668662308</v>
       </c>
       <c r="C180">
-        <v>-1.783090203497388</v>
+        <v>-1.940390274853204</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>-0.2526411300189014</v>
+        <v>0.4840058853188268</v>
       </c>
       <c r="C181">
-        <v>0.2163984003439894</v>
+        <v>-0.8185702726731834</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>-1.009542604794462</v>
+        <v>-0.2673431154463313</v>
       </c>
       <c r="C182">
-        <v>-0.6725842851614218</v>
+        <v>-0.3188886013255306</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>0.05363595856590536</v>
+        <v>-0.846713835083014</v>
       </c>
       <c r="C183">
-        <v>-0.6351285327155628</v>
+        <v>1.24304685262785</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>-1.0594139966388</v>
+        <v>0.3249351325243529</v>
       </c>
       <c r="C184">
-        <v>0.2794648890513302</v>
+        <v>1.429897303719494</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>1.0783508915786</v>
+        <v>-0.1765457387229261</v>
       </c>
       <c r="C185">
-        <v>-1.098735821588773</v>
+        <v>1.173951190096491</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>1.950217178593711</v>
+        <v>-0.0418045765645877</v>
       </c>
       <c r="C186">
-        <v>1.521055382924083</v>
+        <v>-1.512656631877757</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.3121029428582803</v>
+        <v>-0.4021579324013695</v>
       </c>
       <c r="C187">
-        <v>0.3396001989389942</v>
+        <v>0.6024531844046133</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>-1.175304389662243</v>
+        <v>0.4135961557431705</v>
       </c>
       <c r="C188">
-        <v>0.2380357309492989</v>
+        <v>-0.8029327082334169</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-2.39096927433242</v>
+        <v>0.4022717443172377</v>
       </c>
       <c r="C189">
-        <v>-1.549015309944328</v>
+        <v>-0.7734652670723368</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>0.3192910584050046</v>
+        <v>1.103983413769007</v>
       </c>
       <c r="C190">
-        <v>2.364818815787029</v>
+        <v>-1.601572883470669</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>0.9540439267446873</v>
+        <v>0.7115813010788605</v>
       </c>
       <c r="C191">
-        <v>-0.7722730786189397</v>
+        <v>-0.1135941115482375</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>0.1295229966407802</v>
+        <v>-0.03643796730404686</v>
       </c>
       <c r="C192">
-        <v>0.9841665686705982</v>
+        <v>-0.5439292652539806</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-0.4623225345081723</v>
+        <v>-1.321978520850036</v>
       </c>
       <c r="C193">
-        <v>-0.6864412872420893</v>
+        <v>2.435736570563576</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>0.1459299483295041</v>
+        <v>-1.16543669795591</v>
       </c>
       <c r="C194">
-        <v>0.8995905022445292</v>
+        <v>0.5197716225516688</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>-0.2212146288222952</v>
+        <v>0.08670641749331376</v>
       </c>
       <c r="C195">
-        <v>-1.051695650648923</v>
+        <v>-0.7709524250790173</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>0.1441016321456599</v>
+        <v>0.4004412122990353</v>
       </c>
       <c r="C196">
-        <v>0.7733648822319937</v>
+        <v>0.9227977539518533</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>0.1966753843361141</v>
+        <v>0.0926147390767688</v>
       </c>
       <c r="C197">
-        <v>-1.01821713114598</v>
+        <v>0.4633523559539807</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>0.08168773726001839</v>
+        <v>-0.9537053692567444</v>
       </c>
       <c r="C198">
-        <v>-0.9102126905349253</v>
+        <v>-0.4409215588067752</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>1.456712133460655</v>
+        <v>0.1654195311307652</v>
       </c>
       <c r="C199">
-        <v>-0.6993073849049166</v>
+        <v>-0.9550328121323924</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>1.421089268885793</v>
+        <v>-1.572323074254392</v>
       </c>
       <c r="C200">
-        <v>1.402903707713265</v>
+        <v>2.111883864236794</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>2.32133141050344</v>
+        <v>0.8169559341836832</v>
       </c>
       <c r="C201">
-        <v>0.1817315558984967</v>
+        <v>-1.284096518365926</v>
       </c>
     </row>
   </sheetData>
